--- a/main/ig/CodeSystem-tddui-encounter-participant.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-participant.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:15:02+00:00</t>
+    <t>2026-02-06T13:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-participant.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T13:40:54+00:00</t>
+    <t>2026-02-06T14:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-participant.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T15:19:47+00:00</t>
+    <t>2026-02-25T14:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-participant.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T14:12:38+00:00</t>
+    <t>2026-02-26T10:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-participant.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:50:19+00:00</t>
+    <t>2026-02-26T16:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-tddui-encounter-participant.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:06:51+00:00</t>
+    <t>2026-02-27T10:48:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-participant.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-participant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:48:32+00:00</t>
+    <t>2026-02-27T17:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
